--- a/cotizador.xlsx
+++ b/cotizador.xlsx
@@ -490,25 +490,25 @@
         <v>7</v>
       </c>
       <c r="B2" s="3">
-        <v>120624</v>
+        <v>122675</v>
       </c>
       <c r="C2" s="3">
-        <v>154931</v>
+        <v>157565</v>
       </c>
       <c r="D2" s="3">
-        <v>203893</v>
+        <v>207359</v>
       </c>
       <c r="E2" s="3">
-        <v>345656</v>
+        <v>351532</v>
       </c>
       <c r="F2" s="3">
-        <v>596695</v>
+        <v>606839</v>
       </c>
       <c r="G2" s="3">
-        <v>105055</v>
+        <v>106841</v>
       </c>
       <c r="H2" s="3">
-        <v>90618</v>
+        <v>92159</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -516,25 +516,25 @@
         <v>8</v>
       </c>
       <c r="B3" s="3">
-        <v>121150</v>
+        <v>123210</v>
       </c>
       <c r="C3" s="3">
-        <v>166567</v>
+        <v>169399</v>
       </c>
       <c r="D3" s="3">
-        <v>205823</v>
+        <v>209322</v>
       </c>
       <c r="E3" s="3">
-        <v>355171</v>
+        <v>361209</v>
       </c>
       <c r="F3" s="3">
-        <v>598542</v>
+        <v>608717</v>
       </c>
       <c r="G3" s="3">
-        <v>105329</v>
+        <v>107120</v>
       </c>
       <c r="H3" s="3">
-        <v>90976</v>
+        <v>92523</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -542,25 +542,25 @@
         <v>9</v>
       </c>
       <c r="B4" s="3">
-        <v>136281</v>
+        <v>138598</v>
       </c>
       <c r="C4" s="3">
-        <v>166906</v>
+        <v>169743</v>
       </c>
       <c r="D4" s="3">
-        <v>231922</v>
+        <v>235865</v>
       </c>
       <c r="E4" s="3">
-        <v>399768</v>
+        <v>406564</v>
       </c>
       <c r="F4" s="3">
-        <v>673935</v>
+        <v>685392</v>
       </c>
       <c r="G4" s="3">
-        <v>118368</v>
+        <v>120380</v>
       </c>
       <c r="H4" s="3">
-        <v>102617</v>
+        <v>104361</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -568,25 +568,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="3">
-        <v>192366</v>
+        <v>195636</v>
       </c>
       <c r="C5" s="3">
-        <v>275044</v>
+        <v>279720</v>
       </c>
       <c r="D5" s="3">
-        <v>322161</v>
+        <v>327638</v>
       </c>
       <c r="E5" s="3">
-        <v>539865</v>
+        <v>549043</v>
       </c>
       <c r="F5" s="3">
-        <v>803863</v>
+        <v>817529</v>
       </c>
       <c r="G5" s="3">
-        <v>167804</v>
+        <v>170657</v>
       </c>
       <c r="H5" s="3">
-        <v>145958</v>
+        <v>148439</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -594,25 +594,25 @@
         <v>11</v>
       </c>
       <c r="B6" s="3">
-        <v>330763</v>
+        <v>336386</v>
       </c>
       <c r="C6" s="3">
-        <v>440589</v>
+        <v>448079</v>
       </c>
       <c r="D6" s="3">
-        <v>579889</v>
+        <v>589747</v>
       </c>
       <c r="E6" s="3">
-        <v>808257</v>
+        <v>821997</v>
       </c>
       <c r="F6" s="3">
-        <v>1101437</v>
+        <v>1120161</v>
       </c>
       <c r="G6" s="3">
-        <v>289822</v>
+        <v>294749</v>
       </c>
       <c r="H6" s="3">
-        <v>252941</v>
+        <v>257241</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -620,25 +620,25 @@
         <v>12</v>
       </c>
       <c r="B7" s="3">
-        <v>86501</v>
+        <v>87972</v>
       </c>
       <c r="C7" s="3">
-        <v>118437</v>
+        <v>120450</v>
       </c>
       <c r="D7" s="3">
-        <v>154801</v>
+        <v>157433</v>
       </c>
       <c r="E7" s="3">
-        <v>292592</v>
+        <v>297566</v>
       </c>
       <c r="F7" s="3">
-        <v>426878</v>
+        <v>434135</v>
       </c>
       <c r="G7" s="3">
-        <v>82228</v>
+        <v>83626</v>
       </c>
       <c r="H7" s="3">
-        <v>74004</v>
+        <v>75262</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -646,25 +646,25 @@
         <v>13</v>
       </c>
       <c r="B8" s="3">
-        <v>88124</v>
+        <v>89622</v>
       </c>
       <c r="C8" s="3">
-        <v>119607</v>
+        <v>121640</v>
       </c>
       <c r="D8" s="3">
-        <v>154754</v>
+        <v>157385</v>
       </c>
       <c r="E8" s="3">
-        <v>295001</v>
+        <v>300016</v>
       </c>
       <c r="F8" s="3">
-        <v>434802</v>
+        <v>442194</v>
       </c>
       <c r="G8" s="3">
-        <v>81834</v>
+        <v>83225</v>
       </c>
       <c r="H8" s="3">
-        <v>76379</v>
+        <v>77677</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -672,25 +672,25 @@
         <v>14</v>
       </c>
       <c r="B9" s="3">
-        <v>101142</v>
+        <v>102861</v>
       </c>
       <c r="C9" s="3">
-        <v>135393</v>
+        <v>137695</v>
       </c>
       <c r="D9" s="3">
-        <v>178672</v>
+        <v>181709</v>
       </c>
       <c r="E9" s="3">
-        <v>342276</v>
+        <v>348095</v>
       </c>
       <c r="F9" s="3">
-        <v>502049</v>
+        <v>510584</v>
       </c>
       <c r="G9" s="3">
-        <v>95675</v>
+        <v>97301</v>
       </c>
       <c r="H9" s="3">
-        <v>89617</v>
+        <v>91140</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -698,25 +698,25 @@
         <v>15</v>
       </c>
       <c r="B10" s="3">
-        <v>123266</v>
+        <v>125362</v>
       </c>
       <c r="C10" s="3">
-        <v>173279</v>
+        <v>176225</v>
       </c>
       <c r="D10" s="3">
-        <v>212816</v>
+        <v>216434</v>
       </c>
       <c r="E10" s="3">
-        <v>412074</v>
+        <v>419079</v>
       </c>
       <c r="F10" s="3">
-        <v>587481</v>
+        <v>597468</v>
       </c>
       <c r="G10" s="3">
-        <v>114939</v>
+        <v>116893</v>
       </c>
       <c r="H10" s="3">
-        <v>107664</v>
+        <v>109494</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -724,25 +724,25 @@
         <v>16</v>
       </c>
       <c r="B11" s="3">
-        <v>102528</v>
+        <v>104271</v>
       </c>
       <c r="C11" s="3">
-        <v>131688</v>
+        <v>133927</v>
       </c>
       <c r="D11" s="3">
-        <v>173308</v>
+        <v>176254</v>
       </c>
       <c r="E11" s="3">
-        <v>293808</v>
+        <v>298803</v>
       </c>
       <c r="F11" s="3">
-        <v>507189</v>
+        <v>515811</v>
       </c>
       <c r="G11" s="3">
-        <v>89300</v>
+        <v>90818</v>
       </c>
       <c r="H11" s="3">
-        <v>77026</v>
+        <v>78335</v>
       </c>
     </row>
   </sheetData>
